--- a/Hoàng/2025/T5/CT PT VÀ KHAI THÁC HẠ TẦNG KHU CÔNG NGHIỆP ĐÀ NẴNG (74-2025)/DS, DM KSK CÔNG TY PHÁT TRIỂN VÀ KHAI THÁC HẠ TẦNG KCN ĐÀ NẴNG.xlsx
+++ b/Hoàng/2025/T5/CT PT VÀ KHAI THÁC HẠ TẦNG KHU CÔNG NGHIỆP ĐÀ NẴNG (74-2025)/DS, DM KSK CÔNG TY PHÁT TRIỂN VÀ KHAI THÁC HẠ TẦNG KCN ĐÀ NẴNG.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\CT PT VÀ KHAI THÁC HẠ TẦNG KHU CÔNG NGHIỆP ĐÀ NẴNG (74-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DA7266-4D2B-4CC4-8CA3-568EC42CDFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC60BEDB-AA77-4055-8B12-E5DD478AFB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS" sheetId="2" r:id="rId1"/>
-    <sheet name="DM" sheetId="3" r:id="rId2"/>
-    <sheet name="DS VIP" sheetId="5" state="hidden" r:id="rId3"/>
+    <sheet name="DS CŨ" sheetId="6" state="hidden" r:id="rId2"/>
+    <sheet name="DM" sheetId="3" r:id="rId3"/>
+    <sheet name="DS VIP" sheetId="5" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DS!$A$1:$F$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DS!$A$1:$G$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="172">
   <si>
     <t>Họ và tên</t>
   </si>
@@ -411,6 +412,150 @@
   </si>
   <si>
     <t>STT</t>
+  </si>
+  <si>
+    <t>Mã số</t>
+  </si>
+  <si>
+    <t>Họ và tên</t>
+  </si>
+  <si>
+    <t>Thứ tự NV</t>
+  </si>
+  <si>
+    <t>Ngày</t>
+  </si>
+  <si>
+    <t>Tháng</t>
+  </si>
+  <si>
+    <t>Năm</t>
+  </si>
+  <si>
+    <t>NV01</t>
+  </si>
+  <si>
+    <t>NV02</t>
+  </si>
+  <si>
+    <t>NV03</t>
+  </si>
+  <si>
+    <t>NV29</t>
+  </si>
+  <si>
+    <t>NV09</t>
+  </si>
+  <si>
+    <t>NV43</t>
+  </si>
+  <si>
+    <t>NV06</t>
+  </si>
+  <si>
+    <t>NV13</t>
+  </si>
+  <si>
+    <t>NV14</t>
+  </si>
+  <si>
+    <t>NV15</t>
+  </si>
+  <si>
+    <t>NV16</t>
+  </si>
+  <si>
+    <t>NV17</t>
+  </si>
+  <si>
+    <t>NV07</t>
+  </si>
+  <si>
+    <t>NV08</t>
+  </si>
+  <si>
+    <t>NV10</t>
+  </si>
+  <si>
+    <t>NV12</t>
+  </si>
+  <si>
+    <t>NV19</t>
+  </si>
+  <si>
+    <t>NV18</t>
+  </si>
+  <si>
+    <t>NV21</t>
+  </si>
+  <si>
+    <t>NV20</t>
+  </si>
+  <si>
+    <t>NV22</t>
+  </si>
+  <si>
+    <t>NV23</t>
+  </si>
+  <si>
+    <t>NV28</t>
+  </si>
+  <si>
+    <t>NV25</t>
+  </si>
+  <si>
+    <t>NV27</t>
+  </si>
+  <si>
+    <t>NV41</t>
+  </si>
+  <si>
+    <t>NV04</t>
+  </si>
+  <si>
+    <t>NV30</t>
+  </si>
+  <si>
+    <t>NV31</t>
+  </si>
+  <si>
+    <t>NV26</t>
+  </si>
+  <si>
+    <t>NV34</t>
+  </si>
+  <si>
+    <t>NV32</t>
+  </si>
+  <si>
+    <t>NV39</t>
+  </si>
+  <si>
+    <t>NV35</t>
+  </si>
+  <si>
+    <t>NV42</t>
+  </si>
+  <si>
+    <t>NV37</t>
+  </si>
+  <si>
+    <t>NV40</t>
+  </si>
+  <si>
+    <t>NV36</t>
+  </si>
+  <si>
+    <t>Mai Xuân Trung</t>
+  </si>
+  <si>
+    <t>MÃ NV</t>
+  </si>
+  <si>
+    <t>NV44</t>
+  </si>
+  <si>
+    <t>NV45</t>
   </si>
 </sst>
 </file>
@@ -946,18 +1091,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{919FC587-F844-4FA3-8344-E21A9C02D18B}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>123</v>
       </c>
@@ -965,806 +1111,1651 @@
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="C2" s="2" t="str">
+        <f>VLOOKUP(B2,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV01</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1">
         <v>1971</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3" s="2" t="str">
+        <f>VLOOKUP(B3,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV03</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1">
         <v>1983</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="C4" s="2" t="str">
+        <f>VLOOKUP(B4,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1">
         <v>1972</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5" s="2" t="str">
+        <f>VLOOKUP(B5,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV06</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1">
         <v>1972</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6" s="2" t="str">
+        <f>VLOOKUP(B6,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1">
         <v>1975</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="C7" s="2" t="str">
+        <f>VLOOKUP(B7,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1">
         <v>1968</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="C8" s="2" t="str">
+        <f>VLOOKUP(B8,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV21</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1">
         <v>1979</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="C9" s="2" t="str">
+        <f>VLOOKUP(B9,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV26</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1">
         <v>1995</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="C10" s="2" t="str">
+        <f>VLOOKUP(B10,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1">
         <v>1981</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="C11" s="2" t="str">
+        <f>VLOOKUP(B11,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV18</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1">
         <v>1985</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="C12" s="2" t="str">
+        <f>VLOOKUP(B12,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV20</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1">
         <v>1966</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="C13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1">
         <v>1994</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="C14" s="2" t="str">
+        <f>VLOOKUP(B14,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1">
         <v>1983</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="C15" s="2" t="str">
+        <f>VLOOKUP(B15,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV28</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1">
         <v>1993</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="1">
+      <c r="C16" s="2" t="str">
+        <f>VLOOKUP(B16,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV25</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1">
         <v>1973</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="C17" s="2" t="str">
+        <f>VLOOKUP(B17,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV27</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1">
         <v>1973</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="C18" s="2" t="str">
+        <f>VLOOKUP(B18,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV41</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="1">
         <v>2001</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="C19" s="2" t="str">
+        <f>VLOOKUP(B19,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV04</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="1">
         <v>1979</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="1">
+      <c r="C20" s="2" t="str">
+        <f>VLOOKUP(B20,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV30</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="1">
         <v>1977</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="C21" s="2" t="str">
+        <f>VLOOKUP(B21,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV14</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="1">
         <v>1977</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="1">
+      <c r="C22" s="2" t="str">
+        <f>VLOOKUP(B22,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV31</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="1">
         <v>1972</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="1">
+      <c r="C23" s="2" t="str">
+        <f>VLOOKUP(B23,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV35</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="1">
         <v>1971</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="1">
+      <c r="C24" s="2" t="str">
+        <f>VLOOKUP(B24,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV32</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="1">
         <v>1968</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="1">
+      <c r="C25" s="2" t="str">
+        <f>VLOOKUP(B25,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV39</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="1">
         <v>1993</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="1">
+      <c r="C26" s="2" t="str">
+        <f>VLOOKUP(B26,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV37</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="1">
         <v>1987</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="1">
+      <c r="C27" s="2" t="str">
+        <f>VLOOKUP(B27,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV40</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="1">
         <v>1977</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="1">
+      <c r="C28" s="2" t="str">
+        <f>VLOOKUP(B28,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV42</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="1">
         <v>1999</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="1">
+      <c r="C29" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="1">
         <v>2001</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="str">
+        <f>VLOOKUP(B30,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV02</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="1">
+      <c r="E30" s="1">
         <v>1974</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="str">
+        <f>VLOOKUP(B31,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV09</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="1">
+      <c r="E31" s="1">
         <v>1976</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="str">
+        <f>VLOOKUP(B32,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV43</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="1">
+      <c r="E32" s="1">
         <v>1996</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="str">
+        <f>VLOOKUP(B33,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV17</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="1">
+      <c r="E33" s="1">
         <v>1988</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="str">
+        <f>VLOOKUP(B34,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV07</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E34" s="1">
         <v>1975</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="str">
+        <f>VLOOKUP(B35,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV08</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="1">
+      <c r="E35" s="1">
         <v>1987</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="str">
+        <f>VLOOKUP(B36,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV10</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E36" s="1">
         <v>1988</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="str">
+        <f>VLOOKUP(B37,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV12</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="1">
+      <c r="E37" s="1">
         <v>1989</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="str">
+        <f>VLOOKUP(B38,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV16</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D38" s="1">
+      <c r="E38" s="1">
         <v>1984</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="str">
+        <f>VLOOKUP(B39,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV23</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="1">
+      <c r="E39" s="1">
         <v>1975</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="str">
+        <f>VLOOKUP(B40,'DS CŨ'!$B$2:$C$39,2,0)</f>
+        <v>NV34</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="1">
+      <c r="E40" s="1">
         <v>1974</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F40" xr:uid="{919FC587-F844-4FA3-8344-E21A9C02D18B}"/>
+  <autoFilter ref="A1:G40" xr:uid="{919FC587-F844-4FA3-8344-E21A9C02D18B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="59" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59EA13CD-0E27-4F41-A774-BFE97D446567}">
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>145</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="G18">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+      <c r="G19">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>148</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="G20">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="G21">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="G22">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23">
+        <v>22</v>
+      </c>
+      <c r="G23">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24">
+        <v>23</v>
+      </c>
+      <c r="G24">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25">
+        <v>24</v>
+      </c>
+      <c r="G25">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>154</v>
+      </c>
+      <c r="D26">
+        <v>25</v>
+      </c>
+      <c r="G26">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="G27">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28">
+        <v>27</v>
+      </c>
+      <c r="G28">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="G29">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
+        <v>158</v>
+      </c>
+      <c r="D30">
+        <v>29</v>
+      </c>
+      <c r="G30">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="G31">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32">
+        <v>31</v>
+      </c>
+      <c r="G32">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33">
+        <v>32</v>
+      </c>
+      <c r="G33">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34">
+        <v>33</v>
+      </c>
+      <c r="G34">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>163</v>
+      </c>
+      <c r="D35">
+        <v>34</v>
+      </c>
+      <c r="G35">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36">
+        <v>35</v>
+      </c>
+      <c r="G36">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37">
+        <v>36</v>
+      </c>
+      <c r="G37">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" t="s">
+        <v>166</v>
+      </c>
+      <c r="D38">
+        <v>37</v>
+      </c>
+      <c r="G38">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" t="s">
+        <v>167</v>
+      </c>
+      <c r="D39">
+        <v>38</v>
+      </c>
+      <c r="G39">
+        <v>1963</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E70A52B9-70EA-4674-8342-83C5849E4D5A}">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2195,7 +3186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BE0B60-5154-46F3-AEDD-652CE18C3DFF}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Hoàng/2025/T5/CT PT VÀ KHAI THÁC HẠ TẦNG KHU CÔNG NGHIỆP ĐÀ NẴNG (74-2025)/DS, DM KSK CÔNG TY PHÁT TRIỂN VÀ KHAI THÁC HẠ TẦNG KCN ĐÀ NẴNG.xlsx
+++ b/Hoàng/2025/T5/CT PT VÀ KHAI THÁC HẠ TẦNG KHU CÔNG NGHIỆP ĐÀ NẴNG (74-2025)/DS, DM KSK CÔNG TY PHÁT TRIỂN VÀ KHAI THÁC HẠ TẦNG KCN ĐÀ NẴNG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\CT PT VÀ KHAI THÁC HẠ TẦNG KHU CÔNG NGHIỆP ĐÀ NẴNG (74-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC60BEDB-AA77-4055-8B12-E5DD478AFB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE7E706-943C-408D-8731-2EE6AC1E9F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
